--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/region-de-antofagasta.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/region-de-antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,37 +514,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3506-597-CM26</t>
+          <t>1999-3-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>60.103.001-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,6 +569,925 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
+        <v>21079.54</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>3506-145-CM25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>35997.07</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2385-121-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>feb-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-02-25</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>DERCOMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>96.545.450-0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>28715.77</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2386-10-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-03-17</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>61.606.207-7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>15316.59</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1375735-13-CM25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>61.981.250-6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>25256.17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1346284-55-CM25</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mar-2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Comercial Motores de los Andes SpA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>29524.53</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2429-1752-CM25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>42256.94</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2429-1854-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>69.020.300-6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>25864.45</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2385-291-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>17280.12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>650-37-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>may-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>61.814.000-8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>28761.06</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>803-35-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>96.889.440-4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>18851.59</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>650-56-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>61.814.000-8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>28724.26</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4999-127-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.252.500-0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>96.889.440-4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>72908.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1994-65-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>60.511.021-5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>19823.54</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2385-720-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.020.200-K</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>28170.78</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3506-597-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.020.100-3</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>76.349.970-7</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
         <v>29985.76</v>
       </c>
     </row>
